--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6744186046511628</v>
+        <v>0.676923076923077</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6571428571428571</v>
+        <v>0.6642857142857143</v>
       </c>
       <c r="D2">
-        <v>0.3555555555555556</v>
+        <v>0.3481481481481482</v>
       </c>
       <c r="E2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>5</v>
